--- a/12620764 final (1).xlsx
+++ b/12620764 final (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mishty sharma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5184F1-2336-476C-AD06-8D2EFB794E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F758E64-50DD-47DB-87D5-5B86400C4ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>took tuitonn classes for 3 hours</t>
+  </si>
+  <si>
+    <t>loviraj sir was on leave</t>
+  </si>
+  <si>
+    <t>minor project was allotted</t>
   </si>
 </sst>
 </file>
@@ -2437,49 +2443,93 @@
       <c r="A35" s="13">
         <v>46280</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>600</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>200</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>80</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>46281</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="B36" s="14">
+        <v>650</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>200</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>70</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
